--- a/output/06_10/filing_dates_output_v1_with_status_06_10_v1.xlsx
+++ b/output/06_10/filing_dates_output_v1_with_status_06_10_v1.xlsx
@@ -594,9 +594,21 @@
           <t>Income Portfolio I Class P Units</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Multi-Select Securities Fund for Puerto Rico Residents</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Income Portfolio I</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Class P Units</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>

--- a/output/06_10/filing_dates_output_v1_with_status_06_10_v1.xlsx
+++ b/output/06_10/filing_dates_output_v1_with_status_06_10_v1.xlsx
@@ -3738,21 +3738,9 @@
           <t>Everlake Life Insurance Co Choicerate Annuity</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Everlake Life Insurance Co</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Everlake Life Insurance Co</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>ChoiceRate Annuity</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" s="1" t="n">
         <v>46125</v>
